--- a/fx-server/资源/题库/题库（模板）.xlsx
+++ b/fx-server/资源/题库/题库（模板）.xlsx
@@ -95,7 +95,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O240"/>
+  <dimension ref="A1:Q240"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -166,10 +166,20 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>加分</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>减分</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
           <t>备注</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
@@ -229,8 +239,18 @@
           <t>B</t>
         </is>
       </c>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -279,23 +299,17 @@
           <t>2-50mm</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
       <c r="M3" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
       <c r="N3" s="2"/>
-      <c r="O3" s="2" t="n">
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2" t="n">
         <v>19089.0</v>
       </c>
     </row>
@@ -355,6 +369,8 @@
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -412,6 +428,8 @@
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -469,6 +487,8 @@
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
+      <c r="P6" s="2"/>
+      <c r="Q6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -526,6 +546,8 @@
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
+      <c r="P7" s="2"/>
+      <c r="Q7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -583,6 +605,8 @@
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
+      <c r="P8" s="2"/>
+      <c r="Q8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -640,6 +664,8 @@
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -697,6 +723,8 @@
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -754,6 +782,8 @@
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
+      <c r="P11" s="2"/>
+      <c r="Q11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -811,6 +841,8 @@
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
+      <c r="P12" s="2"/>
+      <c r="Q12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -868,6 +900,8 @@
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
+      <c r="P13" s="2"/>
+      <c r="Q13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -925,6 +959,8 @@
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
+      <c r="P14" s="2"/>
+      <c r="Q14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -982,6 +1018,8 @@
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1039,6 +1077,8 @@
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
+      <c r="P16" s="2"/>
+      <c r="Q16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1096,6 +1136,8 @@
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
+      <c r="P17" s="2"/>
+      <c r="Q17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1153,6 +1195,8 @@
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
+      <c r="P18" s="2"/>
+      <c r="Q18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1210,6 +1254,8 @@
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
+      <c r="P19" s="2"/>
+      <c r="Q19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1267,6 +1313,8 @@
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
+      <c r="P20" s="2"/>
+      <c r="Q20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1324,6 +1372,8 @@
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
+      <c r="P21" s="2"/>
+      <c r="Q21" s="2"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1381,6 +1431,8 @@
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
+      <c r="P22" s="2"/>
+      <c r="Q22" s="2"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1438,6 +1490,8 @@
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
+      <c r="P23" s="2"/>
+      <c r="Q23" s="2"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1495,6 +1549,8 @@
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
+      <c r="P24" s="2"/>
+      <c r="Q24" s="2"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1552,6 +1608,8 @@
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
+      <c r="P25" s="2"/>
+      <c r="Q25" s="2"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1609,6 +1667,8 @@
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
+      <c r="P26" s="2"/>
+      <c r="Q26" s="2"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1666,6 +1726,8 @@
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
+      <c r="P27" s="2"/>
+      <c r="Q27" s="2"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1723,6 +1785,8 @@
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
+      <c r="P28" s="2"/>
+      <c r="Q28" s="2"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1780,6 +1844,8 @@
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
+      <c r="P29" s="2"/>
+      <c r="Q29" s="2"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1837,6 +1903,8 @@
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
+      <c r="P30" s="2"/>
+      <c r="Q30" s="2"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1894,6 +1962,8 @@
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
+      <c r="P31" s="2"/>
+      <c r="Q31" s="2"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -1951,6 +2021,8 @@
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
+      <c r="P32" s="2"/>
+      <c r="Q32" s="2"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -2008,6 +2080,8 @@
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
+      <c r="P33" s="2"/>
+      <c r="Q33" s="2"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2065,6 +2139,8 @@
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
+      <c r="P34" s="2"/>
+      <c r="Q34" s="2"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -2122,6 +2198,8 @@
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
+      <c r="P35" s="2"/>
+      <c r="Q35" s="2"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -2179,6 +2257,8 @@
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
+      <c r="P36" s="2"/>
+      <c r="Q36" s="2"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -2236,6 +2316,8 @@
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
+      <c r="P37" s="2"/>
+      <c r="Q37" s="2"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -2293,6 +2375,8 @@
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
+      <c r="P38" s="2"/>
+      <c r="Q38" s="2"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -2350,6 +2434,8 @@
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
+      <c r="P39" s="2"/>
+      <c r="Q39" s="2"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -2407,6 +2493,8 @@
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
+      <c r="P40" s="2"/>
+      <c r="Q40" s="2"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -2464,6 +2552,8 @@
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
+      <c r="P41" s="2"/>
+      <c r="Q41" s="2"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -2521,6 +2611,8 @@
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
+      <c r="P42" s="2"/>
+      <c r="Q42" s="2"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -2578,6 +2670,8 @@
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
+      <c r="P43" s="2"/>
+      <c r="Q43" s="2"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -2635,6 +2729,8 @@
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
+      <c r="P44" s="2"/>
+      <c r="Q44" s="2"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -2692,6 +2788,8 @@
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
+      <c r="P45" s="2"/>
+      <c r="Q45" s="2"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -2749,6 +2847,8 @@
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
+      <c r="P46" s="2"/>
+      <c r="Q46" s="2"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -2806,6 +2906,8 @@
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
+      <c r="P47" s="2"/>
+      <c r="Q47" s="2"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -2863,6 +2965,8 @@
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
+      <c r="P48" s="2"/>
+      <c r="Q48" s="2"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -2920,6 +3024,8 @@
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
+      <c r="P49" s="2"/>
+      <c r="Q49" s="2"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -2977,6 +3083,8 @@
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
+      <c r="P50" s="2"/>
+      <c r="Q50" s="2"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -3034,6 +3142,8 @@
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
+      <c r="P51" s="2"/>
+      <c r="Q51" s="2"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -3091,6 +3201,8 @@
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
+      <c r="P52" s="2"/>
+      <c r="Q52" s="2"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -3148,6 +3260,8 @@
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
+      <c r="P53" s="2"/>
+      <c r="Q53" s="2"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -3205,6 +3319,8 @@
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
+      <c r="P54" s="2"/>
+      <c r="Q54" s="2"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -3262,6 +3378,8 @@
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
+      <c r="P55" s="2"/>
+      <c r="Q55" s="2"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -3319,6 +3437,8 @@
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
+      <c r="P56" s="2"/>
+      <c r="Q56" s="2"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -3376,6 +3496,8 @@
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
+      <c r="P57" s="2"/>
+      <c r="Q57" s="2"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -3433,6 +3555,8 @@
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
+      <c r="P58" s="2"/>
+      <c r="Q58" s="2"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -3490,6 +3614,8 @@
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
+      <c r="P59" s="2"/>
+      <c r="Q59" s="2"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -3547,6 +3673,8 @@
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
+      <c r="P60" s="2"/>
+      <c r="Q60" s="2"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -3577,7 +3705,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>对陕甘宁边区的重点进攻</t>
+          <t>对陕甘宁边区的重点进攻1</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -3595,8 +3723,16 @@
           <t>对山东解放区的重点进攻</t>
         </is>
       </c>
-      <c r="K61" s="2"/>
-      <c r="L61" s="2"/>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
           <t>AD</t>
@@ -3604,6 +3740,10 @@
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
+      <c r="P61" s="2"/>
+      <c r="Q61" s="2" t="n">
+        <v>19383.0</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -3661,6 +3801,8 @@
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
+      <c r="P62" s="2"/>
+      <c r="Q62" s="2"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -3718,6 +3860,8 @@
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
+      <c r="P63" s="2"/>
+      <c r="Q63" s="2"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -3775,6 +3919,8 @@
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
+      <c r="P64" s="2"/>
+      <c r="Q64" s="2"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -3832,6 +3978,8 @@
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
+      <c r="P65" s="2"/>
+      <c r="Q65" s="2"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -3889,6 +4037,8 @@
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
+      <c r="P66" s="2"/>
+      <c r="Q66" s="2"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -3946,6 +4096,8 @@
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
+      <c r="P67" s="2"/>
+      <c r="Q67" s="2"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -4003,6 +4155,8 @@
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
+      <c r="P68" s="2"/>
+      <c r="Q68" s="2"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -4060,6 +4214,8 @@
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
+      <c r="P69" s="2"/>
+      <c r="Q69" s="2"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -4117,6 +4273,8 @@
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
+      <c r="P70" s="2"/>
+      <c r="Q70" s="2"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -4170,6 +4328,8 @@
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
+      <c r="P71" s="2"/>
+      <c r="Q71" s="2"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -4223,6 +4383,8 @@
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
+      <c r="P72" s="2"/>
+      <c r="Q72" s="2"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -4276,6 +4438,8 @@
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
+      <c r="P73" s="2"/>
+      <c r="Q73" s="2"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -4329,6 +4493,8 @@
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
+      <c r="P74" s="2"/>
+      <c r="Q74" s="2"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -4382,7 +4548,9 @@
         </is>
       </c>
       <c r="N75" s="2"/>
-      <c r="O75" s="2" t="n">
+      <c r="O75" s="2"/>
+      <c r="P75" s="2"/>
+      <c r="Q75" s="2" t="n">
         <v>16245.0</v>
       </c>
     </row>
@@ -4438,6 +4606,8 @@
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
+      <c r="P76" s="2"/>
+      <c r="Q76" s="2"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -4491,6 +4661,8 @@
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
+      <c r="P77" s="2"/>
+      <c r="Q77" s="2"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -4544,6 +4716,8 @@
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
+      <c r="P78" s="2"/>
+      <c r="Q78" s="2"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -4597,6 +4771,8 @@
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
+      <c r="P79" s="2"/>
+      <c r="Q79" s="2"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -4650,6 +4826,8 @@
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
+      <c r="P80" s="2"/>
+      <c r="Q80" s="2"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -4691,6 +4869,8 @@
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
+      <c r="P81" s="2"/>
+      <c r="Q81" s="2"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -4732,6 +4912,8 @@
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
+      <c r="P82" s="2"/>
+      <c r="Q82" s="2"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -4773,6 +4955,8 @@
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
+      <c r="P83" s="2"/>
+      <c r="Q83" s="2"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -4814,6 +4998,8 @@
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
+      <c r="P84" s="2"/>
+      <c r="Q84" s="2"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -4855,6 +5041,8 @@
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
+      <c r="P85" s="2"/>
+      <c r="Q85" s="2"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -4896,6 +5084,8 @@
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
+      <c r="P86" s="2"/>
+      <c r="Q86" s="2"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -4937,6 +5127,8 @@
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
+      <c r="P87" s="2"/>
+      <c r="Q87" s="2"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -4978,6 +5170,8 @@
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
+      <c r="P88" s="2"/>
+      <c r="Q88" s="2"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -5019,6 +5213,8 @@
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
+      <c r="P89" s="2"/>
+      <c r="Q89" s="2"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -5060,6 +5256,8 @@
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
+      <c r="P90" s="2"/>
+      <c r="Q90" s="2"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -5117,6 +5315,8 @@
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
+      <c r="P91" s="2"/>
+      <c r="Q91" s="2"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -5174,6 +5374,8 @@
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
+      <c r="P92" s="2"/>
+      <c r="Q92" s="2"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -5231,6 +5433,8 @@
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
+      <c r="P93" s="2"/>
+      <c r="Q93" s="2"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -5292,6 +5496,8 @@
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
+      <c r="P94" s="2"/>
+      <c r="Q94" s="2"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -5349,6 +5555,8 @@
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
+      <c r="P95" s="2"/>
+      <c r="Q95" s="2"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -5406,6 +5614,8 @@
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
+      <c r="P96" s="2"/>
+      <c r="Q96" s="2"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -5471,6 +5681,8 @@
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
+      <c r="P97" s="2"/>
+      <c r="Q97" s="2"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -5532,6 +5744,8 @@
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
+      <c r="P98" s="2"/>
+      <c r="Q98" s="2"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -5589,6 +5803,8 @@
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
+      <c r="P99" s="2"/>
+      <c r="Q99" s="2"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -5646,6 +5862,8 @@
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
+      <c r="P100" s="2"/>
+      <c r="Q100" s="2"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -5703,6 +5921,8 @@
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
+      <c r="P101" s="2"/>
+      <c r="Q101" s="2"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -5760,6 +5980,8 @@
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
+      <c r="P102" s="2"/>
+      <c r="Q102" s="2"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -5817,6 +6039,8 @@
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
+      <c r="P103" s="2"/>
+      <c r="Q103" s="2"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -5874,6 +6098,8 @@
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
+      <c r="P104" s="2"/>
+      <c r="Q104" s="2"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -5931,6 +6157,8 @@
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
+      <c r="P105" s="2"/>
+      <c r="Q105" s="2"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -5988,7 +6216,9 @@
         </is>
       </c>
       <c r="N106" s="2"/>
-      <c r="O106" s="2" t="n">
+      <c r="O106" s="2"/>
+      <c r="P106" s="2"/>
+      <c r="Q106" s="2" t="n">
         <v>16276.0</v>
       </c>
     </row>
@@ -6048,6 +6278,8 @@
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
+      <c r="P107" s="2"/>
+      <c r="Q107" s="2"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -6105,6 +6337,8 @@
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
+      <c r="P108" s="2"/>
+      <c r="Q108" s="2"/>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -6162,6 +6396,8 @@
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
+      <c r="P109" s="2"/>
+      <c r="Q109" s="2"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -6219,6 +6455,8 @@
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
+      <c r="P110" s="2"/>
+      <c r="Q110" s="2"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -6276,6 +6514,8 @@
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
+      <c r="P111" s="2"/>
+      <c r="Q111" s="2"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -6333,6 +6573,8 @@
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
+      <c r="P112" s="2"/>
+      <c r="Q112" s="2"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -6390,6 +6632,8 @@
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
+      <c r="P113" s="2"/>
+      <c r="Q113" s="2"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -6447,6 +6691,8 @@
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
+      <c r="P114" s="2"/>
+      <c r="Q114" s="2"/>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -6504,6 +6750,8 @@
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
+      <c r="P115" s="2"/>
+      <c r="Q115" s="2"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -6561,6 +6809,8 @@
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
+      <c r="P116" s="2"/>
+      <c r="Q116" s="2"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -6618,6 +6868,8 @@
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
+      <c r="P117" s="2"/>
+      <c r="Q117" s="2"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -6675,6 +6927,8 @@
       </c>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
+      <c r="P118" s="2"/>
+      <c r="Q118" s="2"/>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -6732,6 +6986,8 @@
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
+      <c r="P119" s="2"/>
+      <c r="Q119" s="2"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -6789,6 +7045,8 @@
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
+      <c r="P120" s="2"/>
+      <c r="Q120" s="2"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -6846,6 +7104,8 @@
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
+      <c r="P121" s="2"/>
+      <c r="Q121" s="2"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -6903,6 +7163,8 @@
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
+      <c r="P122" s="2"/>
+      <c r="Q122" s="2"/>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -6960,6 +7222,8 @@
       </c>
       <c r="N123" s="2"/>
       <c r="O123" s="2"/>
+      <c r="P123" s="2"/>
+      <c r="Q123" s="2"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -7017,6 +7281,8 @@
       </c>
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
+      <c r="P124" s="2"/>
+      <c r="Q124" s="2"/>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -7074,6 +7340,8 @@
       </c>
       <c r="N125" s="2"/>
       <c r="O125" s="2"/>
+      <c r="P125" s="2"/>
+      <c r="Q125" s="2"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -7135,6 +7403,8 @@
       </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
+      <c r="P126" s="2"/>
+      <c r="Q126" s="2"/>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -7192,6 +7462,8 @@
       </c>
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
+      <c r="P127" s="2"/>
+      <c r="Q127" s="2"/>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -7249,6 +7521,8 @@
       </c>
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
+      <c r="P128" s="2"/>
+      <c r="Q128" s="2"/>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -7306,6 +7580,8 @@
       </c>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
+      <c r="P129" s="2"/>
+      <c r="Q129" s="2"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -7363,6 +7639,8 @@
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
+      <c r="P130" s="2"/>
+      <c r="Q130" s="2"/>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -7420,6 +7698,8 @@
       </c>
       <c r="N131" s="2"/>
       <c r="O131" s="2"/>
+      <c r="P131" s="2"/>
+      <c r="Q131" s="2"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -7477,6 +7757,8 @@
       </c>
       <c r="N132" s="2"/>
       <c r="O132" s="2"/>
+      <c r="P132" s="2"/>
+      <c r="Q132" s="2"/>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -7534,6 +7816,8 @@
       </c>
       <c r="N133" s="2"/>
       <c r="O133" s="2"/>
+      <c r="P133" s="2"/>
+      <c r="Q133" s="2"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -7591,6 +7875,8 @@
       </c>
       <c r="N134" s="2"/>
       <c r="O134" s="2"/>
+      <c r="P134" s="2"/>
+      <c r="Q134" s="2"/>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -7656,6 +7942,8 @@
       </c>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
+      <c r="P135" s="2"/>
+      <c r="Q135" s="2"/>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -7717,6 +8005,8 @@
       </c>
       <c r="N136" s="2"/>
       <c r="O136" s="2"/>
+      <c r="P136" s="2"/>
+      <c r="Q136" s="2"/>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -7782,6 +8072,8 @@
       </c>
       <c r="N137" s="2"/>
       <c r="O137" s="2"/>
+      <c r="P137" s="2"/>
+      <c r="Q137" s="2"/>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -7839,6 +8131,8 @@
       </c>
       <c r="N138" s="2"/>
       <c r="O138" s="2"/>
+      <c r="P138" s="2"/>
+      <c r="Q138" s="2"/>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -7896,6 +8190,8 @@
       </c>
       <c r="N139" s="2"/>
       <c r="O139" s="2"/>
+      <c r="P139" s="2"/>
+      <c r="Q139" s="2"/>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -7953,6 +8249,8 @@
       </c>
       <c r="N140" s="2"/>
       <c r="O140" s="2"/>
+      <c r="P140" s="2"/>
+      <c r="Q140" s="2"/>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -8010,6 +8308,8 @@
       </c>
       <c r="N141" s="2"/>
       <c r="O141" s="2"/>
+      <c r="P141" s="2"/>
+      <c r="Q141" s="2"/>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -8067,6 +8367,8 @@
       </c>
       <c r="N142" s="2"/>
       <c r="O142" s="2"/>
+      <c r="P142" s="2"/>
+      <c r="Q142" s="2"/>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -8124,6 +8426,8 @@
       </c>
       <c r="N143" s="2"/>
       <c r="O143" s="2"/>
+      <c r="P143" s="2"/>
+      <c r="Q143" s="2"/>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -8181,6 +8485,8 @@
       </c>
       <c r="N144" s="2"/>
       <c r="O144" s="2"/>
+      <c r="P144" s="2"/>
+      <c r="Q144" s="2"/>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -8238,6 +8544,8 @@
       </c>
       <c r="N145" s="2"/>
       <c r="O145" s="2"/>
+      <c r="P145" s="2"/>
+      <c r="Q145" s="2"/>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -8295,6 +8603,8 @@
       </c>
       <c r="N146" s="2"/>
       <c r="O146" s="2"/>
+      <c r="P146" s="2"/>
+      <c r="Q146" s="2"/>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -8352,6 +8662,8 @@
       </c>
       <c r="N147" s="2"/>
       <c r="O147" s="2"/>
+      <c r="P147" s="2"/>
+      <c r="Q147" s="2"/>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -8409,6 +8721,8 @@
       </c>
       <c r="N148" s="2"/>
       <c r="O148" s="2"/>
+      <c r="P148" s="2"/>
+      <c r="Q148" s="2"/>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
@@ -8466,6 +8780,8 @@
       </c>
       <c r="N149" s="2"/>
       <c r="O149" s="2"/>
+      <c r="P149" s="2"/>
+      <c r="Q149" s="2"/>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -8523,6 +8839,8 @@
       </c>
       <c r="N150" s="2"/>
       <c r="O150" s="2"/>
+      <c r="P150" s="2"/>
+      <c r="Q150" s="2"/>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -8580,6 +8898,8 @@
       </c>
       <c r="N151" s="2"/>
       <c r="O151" s="2"/>
+      <c r="P151" s="2"/>
+      <c r="Q151" s="2"/>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -8637,6 +8957,8 @@
       </c>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
+      <c r="P152" s="2"/>
+      <c r="Q152" s="2"/>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
@@ -8694,6 +9016,8 @@
       </c>
       <c r="N153" s="2"/>
       <c r="O153" s="2"/>
+      <c r="P153" s="2"/>
+      <c r="Q153" s="2"/>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -8751,6 +9075,8 @@
       </c>
       <c r="N154" s="2"/>
       <c r="O154" s="2"/>
+      <c r="P154" s="2"/>
+      <c r="Q154" s="2"/>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
@@ -8808,6 +9134,8 @@
       </c>
       <c r="N155" s="2"/>
       <c r="O155" s="2"/>
+      <c r="P155" s="2"/>
+      <c r="Q155" s="2"/>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
@@ -8865,6 +9193,8 @@
       </c>
       <c r="N156" s="2"/>
       <c r="O156" s="2"/>
+      <c r="P156" s="2"/>
+      <c r="Q156" s="2"/>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
@@ -8922,6 +9252,8 @@
       </c>
       <c r="N157" s="2"/>
       <c r="O157" s="2"/>
+      <c r="P157" s="2"/>
+      <c r="Q157" s="2"/>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
@@ -8979,6 +9311,8 @@
       </c>
       <c r="N158" s="2"/>
       <c r="O158" s="2"/>
+      <c r="P158" s="2"/>
+      <c r="Q158" s="2"/>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
@@ -9036,6 +9370,8 @@
       </c>
       <c r="N159" s="2"/>
       <c r="O159" s="2"/>
+      <c r="P159" s="2"/>
+      <c r="Q159" s="2"/>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -9093,6 +9429,8 @@
       </c>
       <c r="N160" s="2"/>
       <c r="O160" s="2"/>
+      <c r="P160" s="2"/>
+      <c r="Q160" s="2"/>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
@@ -9146,6 +9484,8 @@
       </c>
       <c r="N161" s="2"/>
       <c r="O161" s="2"/>
+      <c r="P161" s="2"/>
+      <c r="Q161" s="2"/>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
@@ -9199,6 +9539,8 @@
       </c>
       <c r="N162" s="2"/>
       <c r="O162" s="2"/>
+      <c r="P162" s="2"/>
+      <c r="Q162" s="2"/>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
@@ -9252,6 +9594,8 @@
       </c>
       <c r="N163" s="2"/>
       <c r="O163" s="2"/>
+      <c r="P163" s="2"/>
+      <c r="Q163" s="2"/>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
@@ -9305,6 +9649,8 @@
       </c>
       <c r="N164" s="2"/>
       <c r="O164" s="2"/>
+      <c r="P164" s="2"/>
+      <c r="Q164" s="2"/>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
@@ -9358,6 +9704,8 @@
       </c>
       <c r="N165" s="2"/>
       <c r="O165" s="2"/>
+      <c r="P165" s="2"/>
+      <c r="Q165" s="2"/>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
@@ -9411,6 +9759,8 @@
       </c>
       <c r="N166" s="2"/>
       <c r="O166" s="2"/>
+      <c r="P166" s="2"/>
+      <c r="Q166" s="2"/>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
@@ -9464,6 +9814,8 @@
       </c>
       <c r="N167" s="2"/>
       <c r="O167" s="2"/>
+      <c r="P167" s="2"/>
+      <c r="Q167" s="2"/>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
@@ -9517,6 +9869,8 @@
       </c>
       <c r="N168" s="2"/>
       <c r="O168" s="2"/>
+      <c r="P168" s="2"/>
+      <c r="Q168" s="2"/>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
@@ -9574,6 +9928,8 @@
       </c>
       <c r="N169" s="2"/>
       <c r="O169" s="2"/>
+      <c r="P169" s="2"/>
+      <c r="Q169" s="2"/>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
@@ -9627,6 +9983,8 @@
       </c>
       <c r="N170" s="2"/>
       <c r="O170" s="2"/>
+      <c r="P170" s="2"/>
+      <c r="Q170" s="2"/>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
@@ -9680,6 +10038,8 @@
       </c>
       <c r="N171" s="2"/>
       <c r="O171" s="2"/>
+      <c r="P171" s="2"/>
+      <c r="Q171" s="2"/>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
@@ -9733,6 +10093,8 @@
       </c>
       <c r="N172" s="2"/>
       <c r="O172" s="2"/>
+      <c r="P172" s="2"/>
+      <c r="Q172" s="2"/>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
@@ -9786,6 +10148,8 @@
       </c>
       <c r="N173" s="2"/>
       <c r="O173" s="2"/>
+      <c r="P173" s="2"/>
+      <c r="Q173" s="2"/>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
@@ -9839,6 +10203,8 @@
       </c>
       <c r="N174" s="2"/>
       <c r="O174" s="2"/>
+      <c r="P174" s="2"/>
+      <c r="Q174" s="2"/>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
@@ -9892,6 +10258,8 @@
       </c>
       <c r="N175" s="2"/>
       <c r="O175" s="2"/>
+      <c r="P175" s="2"/>
+      <c r="Q175" s="2"/>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
@@ -9945,6 +10313,8 @@
       </c>
       <c r="N176" s="2"/>
       <c r="O176" s="2"/>
+      <c r="P176" s="2"/>
+      <c r="Q176" s="2"/>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
@@ -9998,6 +10368,8 @@
       </c>
       <c r="N177" s="2"/>
       <c r="O177" s="2"/>
+      <c r="P177" s="2"/>
+      <c r="Q177" s="2"/>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
@@ -10051,6 +10423,8 @@
       </c>
       <c r="N178" s="2"/>
       <c r="O178" s="2"/>
+      <c r="P178" s="2"/>
+      <c r="Q178" s="2"/>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
@@ -10104,6 +10478,8 @@
       </c>
       <c r="N179" s="2"/>
       <c r="O179" s="2"/>
+      <c r="P179" s="2"/>
+      <c r="Q179" s="2"/>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
@@ -10157,6 +10533,8 @@
       </c>
       <c r="N180" s="2"/>
       <c r="O180" s="2"/>
+      <c r="P180" s="2"/>
+      <c r="Q180" s="2"/>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
@@ -10210,6 +10588,8 @@
       </c>
       <c r="N181" s="2"/>
       <c r="O181" s="2"/>
+      <c r="P181" s="2"/>
+      <c r="Q181" s="2"/>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
@@ -10263,6 +10643,8 @@
       </c>
       <c r="N182" s="2"/>
       <c r="O182" s="2"/>
+      <c r="P182" s="2"/>
+      <c r="Q182" s="2"/>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
@@ -10316,6 +10698,8 @@
       </c>
       <c r="N183" s="2"/>
       <c r="O183" s="2"/>
+      <c r="P183" s="2"/>
+      <c r="Q183" s="2"/>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
@@ -10369,6 +10753,8 @@
       </c>
       <c r="N184" s="2"/>
       <c r="O184" s="2"/>
+      <c r="P184" s="2"/>
+      <c r="Q184" s="2"/>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
@@ -10422,6 +10808,8 @@
       </c>
       <c r="N185" s="2"/>
       <c r="O185" s="2"/>
+      <c r="P185" s="2"/>
+      <c r="Q185" s="2"/>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
@@ -10475,6 +10863,8 @@
       </c>
       <c r="N186" s="2"/>
       <c r="O186" s="2"/>
+      <c r="P186" s="2"/>
+      <c r="Q186" s="2"/>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
@@ -10528,6 +10918,8 @@
       </c>
       <c r="N187" s="2"/>
       <c r="O187" s="2"/>
+      <c r="P187" s="2"/>
+      <c r="Q187" s="2"/>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
@@ -10581,6 +10973,8 @@
       </c>
       <c r="N188" s="2"/>
       <c r="O188" s="2"/>
+      <c r="P188" s="2"/>
+      <c r="Q188" s="2"/>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
@@ -10634,6 +11028,8 @@
       </c>
       <c r="N189" s="2"/>
       <c r="O189" s="2"/>
+      <c r="P189" s="2"/>
+      <c r="Q189" s="2"/>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
@@ -10683,6 +11079,8 @@
       </c>
       <c r="N190" s="2"/>
       <c r="O190" s="2"/>
+      <c r="P190" s="2"/>
+      <c r="Q190" s="2"/>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
@@ -10740,6 +11138,8 @@
       </c>
       <c r="N191" s="2"/>
       <c r="O191" s="2"/>
+      <c r="P191" s="2"/>
+      <c r="Q191" s="2"/>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
@@ -10797,6 +11197,8 @@
       </c>
       <c r="N192" s="2"/>
       <c r="O192" s="2"/>
+      <c r="P192" s="2"/>
+      <c r="Q192" s="2"/>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
@@ -10854,6 +11256,8 @@
       </c>
       <c r="N193" s="2"/>
       <c r="O193" s="2"/>
+      <c r="P193" s="2"/>
+      <c r="Q193" s="2"/>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
@@ -10911,6 +11315,8 @@
       </c>
       <c r="N194" s="2"/>
       <c r="O194" s="2"/>
+      <c r="P194" s="2"/>
+      <c r="Q194" s="2"/>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
@@ -10964,6 +11370,8 @@
       </c>
       <c r="N195" s="2"/>
       <c r="O195" s="2"/>
+      <c r="P195" s="2"/>
+      <c r="Q195" s="2"/>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
@@ -11017,6 +11425,8 @@
       </c>
       <c r="N196" s="2"/>
       <c r="O196" s="2"/>
+      <c r="P196" s="2"/>
+      <c r="Q196" s="2"/>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
@@ -11066,6 +11476,8 @@
       </c>
       <c r="N197" s="2"/>
       <c r="O197" s="2"/>
+      <c r="P197" s="2"/>
+      <c r="Q197" s="2"/>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
@@ -11123,6 +11535,8 @@
       </c>
       <c r="N198" s="2"/>
       <c r="O198" s="2"/>
+      <c r="P198" s="2"/>
+      <c r="Q198" s="2"/>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
@@ -11176,6 +11590,8 @@
       </c>
       <c r="N199" s="2"/>
       <c r="O199" s="2"/>
+      <c r="P199" s="2"/>
+      <c r="Q199" s="2"/>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
@@ -11229,6 +11645,8 @@
       </c>
       <c r="N200" s="2"/>
       <c r="O200" s="2"/>
+      <c r="P200" s="2"/>
+      <c r="Q200" s="2"/>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
@@ -11286,6 +11704,8 @@
       </c>
       <c r="N201" s="2"/>
       <c r="O201" s="2"/>
+      <c r="P201" s="2"/>
+      <c r="Q201" s="2"/>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
@@ -11343,6 +11763,8 @@
       </c>
       <c r="N202" s="2"/>
       <c r="O202" s="2"/>
+      <c r="P202" s="2"/>
+      <c r="Q202" s="2"/>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
@@ -11400,6 +11822,8 @@
       </c>
       <c r="N203" s="2"/>
       <c r="O203" s="2"/>
+      <c r="P203" s="2"/>
+      <c r="Q203" s="2"/>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
@@ -11457,6 +11881,8 @@
       </c>
       <c r="N204" s="2"/>
       <c r="O204" s="2"/>
+      <c r="P204" s="2"/>
+      <c r="Q204" s="2"/>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
@@ -11514,6 +11940,8 @@
       </c>
       <c r="N205" s="2"/>
       <c r="O205" s="2"/>
+      <c r="P205" s="2"/>
+      <c r="Q205" s="2"/>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
@@ -11571,6 +11999,8 @@
       </c>
       <c r="N206" s="2"/>
       <c r="O206" s="2"/>
+      <c r="P206" s="2"/>
+      <c r="Q206" s="2"/>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
@@ -11628,6 +12058,8 @@
       </c>
       <c r="N207" s="2"/>
       <c r="O207" s="2"/>
+      <c r="P207" s="2"/>
+      <c r="Q207" s="2"/>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
@@ -11685,6 +12117,8 @@
       </c>
       <c r="N208" s="2"/>
       <c r="O208" s="2"/>
+      <c r="P208" s="2"/>
+      <c r="Q208" s="2"/>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
@@ -11742,6 +12176,8 @@
       </c>
       <c r="N209" s="2"/>
       <c r="O209" s="2"/>
+      <c r="P209" s="2"/>
+      <c r="Q209" s="2"/>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
@@ -11799,6 +12235,8 @@
       </c>
       <c r="N210" s="2"/>
       <c r="O210" s="2"/>
+      <c r="P210" s="2"/>
+      <c r="Q210" s="2"/>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
@@ -11856,6 +12294,8 @@
       </c>
       <c r="N211" s="2"/>
       <c r="O211" s="2"/>
+      <c r="P211" s="2"/>
+      <c r="Q211" s="2"/>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
@@ -11913,6 +12353,8 @@
       </c>
       <c r="N212" s="2"/>
       <c r="O212" s="2"/>
+      <c r="P212" s="2"/>
+      <c r="Q212" s="2"/>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
@@ -11970,6 +12412,8 @@
       </c>
       <c r="N213" s="2"/>
       <c r="O213" s="2"/>
+      <c r="P213" s="2"/>
+      <c r="Q213" s="2"/>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
@@ -12027,6 +12471,8 @@
       </c>
       <c r="N214" s="2"/>
       <c r="O214" s="2"/>
+      <c r="P214" s="2"/>
+      <c r="Q214" s="2"/>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
@@ -12088,6 +12534,8 @@
       </c>
       <c r="N215" s="2"/>
       <c r="O215" s="2"/>
+      <c r="P215" s="2"/>
+      <c r="Q215" s="2"/>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
@@ -12145,6 +12593,8 @@
       </c>
       <c r="N216" s="2"/>
       <c r="O216" s="2"/>
+      <c r="P216" s="2"/>
+      <c r="Q216" s="2"/>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
@@ -12202,6 +12652,8 @@
       </c>
       <c r="N217" s="2"/>
       <c r="O217" s="2"/>
+      <c r="P217" s="2"/>
+      <c r="Q217" s="2"/>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
@@ -12259,6 +12711,8 @@
       </c>
       <c r="N218" s="2"/>
       <c r="O218" s="2"/>
+      <c r="P218" s="2"/>
+      <c r="Q218" s="2"/>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
@@ -12320,6 +12774,8 @@
       </c>
       <c r="N219" s="2"/>
       <c r="O219" s="2"/>
+      <c r="P219" s="2"/>
+      <c r="Q219" s="2"/>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
@@ -12377,6 +12833,8 @@
       </c>
       <c r="N220" s="2"/>
       <c r="O220" s="2"/>
+      <c r="P220" s="2"/>
+      <c r="Q220" s="2"/>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
@@ -12418,6 +12876,8 @@
       </c>
       <c r="N221" s="2"/>
       <c r="O221" s="2"/>
+      <c r="P221" s="2"/>
+      <c r="Q221" s="2"/>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
@@ -12459,6 +12919,8 @@
       </c>
       <c r="N222" s="2"/>
       <c r="O222" s="2"/>
+      <c r="P222" s="2"/>
+      <c r="Q222" s="2"/>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
@@ -12500,6 +12962,8 @@
       </c>
       <c r="N223" s="2"/>
       <c r="O223" s="2"/>
+      <c r="P223" s="2"/>
+      <c r="Q223" s="2"/>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
@@ -12541,6 +13005,8 @@
       </c>
       <c r="N224" s="2"/>
       <c r="O224" s="2"/>
+      <c r="P224" s="2"/>
+      <c r="Q224" s="2"/>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
@@ -12582,6 +13048,8 @@
       </c>
       <c r="N225" s="2"/>
       <c r="O225" s="2"/>
+      <c r="P225" s="2"/>
+      <c r="Q225" s="2"/>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
@@ -12623,6 +13091,8 @@
       </c>
       <c r="N226" s="2"/>
       <c r="O226" s="2"/>
+      <c r="P226" s="2"/>
+      <c r="Q226" s="2"/>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
@@ -12664,6 +13134,8 @@
       </c>
       <c r="N227" s="2"/>
       <c r="O227" s="2"/>
+      <c r="P227" s="2"/>
+      <c r="Q227" s="2"/>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
@@ -12705,6 +13177,8 @@
       </c>
       <c r="N228" s="2"/>
       <c r="O228" s="2"/>
+      <c r="P228" s="2"/>
+      <c r="Q228" s="2"/>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
@@ -12746,6 +13220,8 @@
       </c>
       <c r="N229" s="2"/>
       <c r="O229" s="2"/>
+      <c r="P229" s="2"/>
+      <c r="Q229" s="2"/>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
@@ -12787,6 +13263,8 @@
       </c>
       <c r="N230" s="2"/>
       <c r="O230" s="2"/>
+      <c r="P230" s="2"/>
+      <c r="Q230" s="2"/>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
@@ -12828,6 +13306,8 @@
       </c>
       <c r="N231" s="2"/>
       <c r="O231" s="2"/>
+      <c r="P231" s="2"/>
+      <c r="Q231" s="2"/>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
@@ -12869,6 +13349,8 @@
       </c>
       <c r="N232" s="2"/>
       <c r="O232" s="2"/>
+      <c r="P232" s="2"/>
+      <c r="Q232" s="2"/>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
@@ -12910,6 +13392,8 @@
       </c>
       <c r="N233" s="2"/>
       <c r="O233" s="2"/>
+      <c r="P233" s="2"/>
+      <c r="Q233" s="2"/>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
@@ -12951,6 +13435,8 @@
       </c>
       <c r="N234" s="2"/>
       <c r="O234" s="2"/>
+      <c r="P234" s="2"/>
+      <c r="Q234" s="2"/>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
@@ -12992,6 +13478,8 @@
       </c>
       <c r="N235" s="2"/>
       <c r="O235" s="2"/>
+      <c r="P235" s="2"/>
+      <c r="Q235" s="2"/>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
@@ -13033,6 +13521,8 @@
       </c>
       <c r="N236" s="2"/>
       <c r="O236" s="2"/>
+      <c r="P236" s="2"/>
+      <c r="Q236" s="2"/>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
@@ -13074,6 +13564,8 @@
       </c>
       <c r="N237" s="2"/>
       <c r="O237" s="2"/>
+      <c r="P237" s="2"/>
+      <c r="Q237" s="2"/>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
@@ -13115,6 +13607,8 @@
       </c>
       <c r="N238" s="2"/>
       <c r="O238" s="2"/>
+      <c r="P238" s="2"/>
+      <c r="Q238" s="2"/>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
@@ -13156,6 +13650,8 @@
       </c>
       <c r="N239" s="2"/>
       <c r="O239" s="2"/>
+      <c r="P239" s="2"/>
+      <c r="Q239" s="2"/>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
@@ -13197,6 +13693,8 @@
       </c>
       <c r="N240" s="2"/>
       <c r="O240" s="2"/>
+      <c r="P240" s="2"/>
+      <c r="Q240" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/fx-server/资源/题库/题库（模板）.xlsx
+++ b/fx-server/资源/题库/题库（模板）.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10703"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10810"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zhangshuaiqiang/Desktop/code/competition-app/fx-server/资源/题库/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BC4079D-3045-0546-B193-1F3E19823528}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9FE6E98-D8D8-D442-97E7-0E8624D3CBC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="27940" windowHeight="12520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8538,9 +8538,7 @@
         <v>176</v>
       </c>
       <c r="N121" s="2"/>
-      <c r="O121" s="2">
-        <v>4</v>
-      </c>
+      <c r="O121" s="2"/>
       <c r="P121" s="2"/>
       <c r="Q121" s="2"/>
     </row>

--- a/fx-server/资源/题库/题库（模板）.xlsx
+++ b/fx-server/资源/题库/题库（模板）.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10914"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zhangshuaiqiang/Desktop/code/competition-app/fx-server/资源/题库/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9FE6E98-D8D8-D442-97E7-0E8624D3CBC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0965FB04-CD43-B04A-B454-2F7B3B47FFB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="27940" windowHeight="12520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="27940" windowHeight="18500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0" sheetId="1" r:id="rId1"/>
@@ -3187,9 +3187,6 @@
     <t>拥护祖国统一和致力于中华民族伟大复兴的爱国者</t>
   </si>
   <si>
-    <t>7.3</t>
-  </si>
-  <si>
     <t>风险题30分</t>
   </si>
   <si>
@@ -3314,6 +3311,10 @@
   </si>
   <si>
     <t>平型关。</t>
+  </si>
+  <si>
+    <t>8</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -3390,7 +3391,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3398,6 +3399,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -12386,21 +12388,21 @@
       <c r="Q220" s="2"/>
     </row>
     <row r="221" spans="1:17" ht="15">
-      <c r="A221" s="2" t="s">
+      <c r="A221" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B221" s="2" t="s">
         <v>1050</v>
       </c>
-      <c r="B221" s="2" t="s">
+      <c r="C221" s="2" t="s">
         <v>1051</v>
-      </c>
-      <c r="C221" s="2" t="s">
-        <v>1052</v>
       </c>
       <c r="D221" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E221" s="2"/>
       <c r="F221" s="2" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="G221" s="2"/>
       <c r="H221" s="2"/>
@@ -12409,7 +12411,7 @@
       <c r="K221" s="2"/>
       <c r="L221" s="2"/>
       <c r="M221" s="2" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="N221" s="2"/>
       <c r="O221" s="2"/>
@@ -12417,21 +12419,21 @@
       <c r="Q221" s="2"/>
     </row>
     <row r="222" spans="1:17" ht="15">
-      <c r="A222" s="2" t="s">
+      <c r="A222" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B222" s="2" t="s">
         <v>1050</v>
       </c>
-      <c r="B222" s="2" t="s">
+      <c r="C222" s="2" t="s">
         <v>1051</v>
-      </c>
-      <c r="C222" s="2" t="s">
-        <v>1052</v>
       </c>
       <c r="D222" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E222" s="2"/>
       <c r="F222" s="2" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="G222" s="2"/>
       <c r="H222" s="2"/>
@@ -12440,7 +12442,7 @@
       <c r="K222" s="2"/>
       <c r="L222" s="2"/>
       <c r="M222" s="2" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="N222" s="2"/>
       <c r="O222" s="2"/>
@@ -12448,21 +12450,21 @@
       <c r="Q222" s="2"/>
     </row>
     <row r="223" spans="1:17" ht="15">
-      <c r="A223" s="2" t="s">
+      <c r="A223" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B223" s="2" t="s">
         <v>1050</v>
       </c>
-      <c r="B223" s="2" t="s">
+      <c r="C223" s="2" t="s">
         <v>1051</v>
-      </c>
-      <c r="C223" s="2" t="s">
-        <v>1052</v>
       </c>
       <c r="D223" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E223" s="2"/>
       <c r="F223" s="2" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="G223" s="2"/>
       <c r="H223" s="2"/>
@@ -12471,7 +12473,7 @@
       <c r="K223" s="2"/>
       <c r="L223" s="2"/>
       <c r="M223" s="2" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="N223" s="2"/>
       <c r="O223" s="2"/>
@@ -12479,21 +12481,21 @@
       <c r="Q223" s="2"/>
     </row>
     <row r="224" spans="1:17" ht="15">
-      <c r="A224" s="2" t="s">
+      <c r="A224" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B224" s="2" t="s">
         <v>1050</v>
       </c>
-      <c r="B224" s="2" t="s">
+      <c r="C224" s="2" t="s">
         <v>1051</v>
-      </c>
-      <c r="C224" s="2" t="s">
-        <v>1052</v>
       </c>
       <c r="D224" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E224" s="2"/>
       <c r="F224" s="2" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="G224" s="2"/>
       <c r="H224" s="2"/>
@@ -12502,7 +12504,7 @@
       <c r="K224" s="2"/>
       <c r="L224" s="2"/>
       <c r="M224" s="2" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="N224" s="2"/>
       <c r="O224" s="2"/>
@@ -12510,21 +12512,21 @@
       <c r="Q224" s="2"/>
     </row>
     <row r="225" spans="1:17" ht="15">
-      <c r="A225" s="2" t="s">
+      <c r="A225" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B225" s="2" t="s">
         <v>1050</v>
       </c>
-      <c r="B225" s="2" t="s">
+      <c r="C225" s="2" t="s">
         <v>1051</v>
-      </c>
-      <c r="C225" s="2" t="s">
-        <v>1052</v>
       </c>
       <c r="D225" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E225" s="2"/>
       <c r="F225" s="2" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="G225" s="2"/>
       <c r="H225" s="2"/>
@@ -12533,7 +12535,7 @@
       <c r="K225" s="2"/>
       <c r="L225" s="2"/>
       <c r="M225" s="2" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="N225" s="2"/>
       <c r="O225" s="2"/>
@@ -12541,21 +12543,21 @@
       <c r="Q225" s="2"/>
     </row>
     <row r="226" spans="1:17" ht="15">
-      <c r="A226" s="2" t="s">
+      <c r="A226" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B226" s="2" t="s">
         <v>1050</v>
       </c>
-      <c r="B226" s="2" t="s">
+      <c r="C226" s="2" t="s">
         <v>1051</v>
-      </c>
-      <c r="C226" s="2" t="s">
-        <v>1052</v>
       </c>
       <c r="D226" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E226" s="2"/>
       <c r="F226" s="2" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="G226" s="2"/>
       <c r="H226" s="2"/>
@@ -12564,7 +12566,7 @@
       <c r="K226" s="2"/>
       <c r="L226" s="2"/>
       <c r="M226" s="2" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="N226" s="2"/>
       <c r="O226" s="2"/>
@@ -12572,21 +12574,21 @@
       <c r="Q226" s="2"/>
     </row>
     <row r="227" spans="1:17" ht="15">
-      <c r="A227" s="2" t="s">
+      <c r="A227" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B227" s="2" t="s">
         <v>1050</v>
       </c>
-      <c r="B227" s="2" t="s">
+      <c r="C227" s="2" t="s">
         <v>1051</v>
-      </c>
-      <c r="C227" s="2" t="s">
-        <v>1052</v>
       </c>
       <c r="D227" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E227" s="2"/>
       <c r="F227" s="2" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="G227" s="2"/>
       <c r="H227" s="2"/>
@@ -12595,7 +12597,7 @@
       <c r="K227" s="2"/>
       <c r="L227" s="2"/>
       <c r="M227" s="2" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="N227" s="2"/>
       <c r="O227" s="2"/>
@@ -12603,21 +12605,21 @@
       <c r="Q227" s="2"/>
     </row>
     <row r="228" spans="1:17" ht="15">
-      <c r="A228" s="2" t="s">
+      <c r="A228" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B228" s="2" t="s">
         <v>1050</v>
       </c>
-      <c r="B228" s="2" t="s">
+      <c r="C228" s="2" t="s">
         <v>1051</v>
-      </c>
-      <c r="C228" s="2" t="s">
-        <v>1052</v>
       </c>
       <c r="D228" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E228" s="2"/>
       <c r="F228" s="2" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="G228" s="2"/>
       <c r="H228" s="2"/>
@@ -12626,7 +12628,7 @@
       <c r="K228" s="2"/>
       <c r="L228" s="2"/>
       <c r="M228" s="2" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="N228" s="2"/>
       <c r="O228" s="2"/>
@@ -12634,21 +12636,21 @@
       <c r="Q228" s="2"/>
     </row>
     <row r="229" spans="1:17" ht="15">
-      <c r="A229" s="2" t="s">
+      <c r="A229" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B229" s="2" t="s">
         <v>1050</v>
       </c>
-      <c r="B229" s="2" t="s">
+      <c r="C229" s="2" t="s">
         <v>1051</v>
-      </c>
-      <c r="C229" s="2" t="s">
-        <v>1052</v>
       </c>
       <c r="D229" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E229" s="2"/>
       <c r="F229" s="2" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="G229" s="2"/>
       <c r="H229" s="2"/>
@@ -12657,7 +12659,7 @@
       <c r="K229" s="2"/>
       <c r="L229" s="2"/>
       <c r="M229" s="2" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="N229" s="2"/>
       <c r="O229" s="2"/>
@@ -12665,21 +12667,21 @@
       <c r="Q229" s="2"/>
     </row>
     <row r="230" spans="1:17" ht="15">
-      <c r="A230" s="2" t="s">
+      <c r="A230" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B230" s="2" t="s">
         <v>1050</v>
       </c>
-      <c r="B230" s="2" t="s">
+      <c r="C230" s="2" t="s">
         <v>1051</v>
-      </c>
-      <c r="C230" s="2" t="s">
-        <v>1052</v>
       </c>
       <c r="D230" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E230" s="2"/>
       <c r="F230" s="2" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="G230" s="2"/>
       <c r="H230" s="2"/>
@@ -12688,7 +12690,7 @@
       <c r="K230" s="2"/>
       <c r="L230" s="2"/>
       <c r="M230" s="2" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="N230" s="2"/>
       <c r="O230" s="2"/>
@@ -12696,21 +12698,21 @@
       <c r="Q230" s="2"/>
     </row>
     <row r="231" spans="1:17" ht="15">
-      <c r="A231" s="2" t="s">
+      <c r="A231" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B231" s="2" t="s">
         <v>1050</v>
       </c>
-      <c r="B231" s="2" t="s">
+      <c r="C231" s="2" t="s">
         <v>1051</v>
-      </c>
-      <c r="C231" s="2" t="s">
-        <v>1052</v>
       </c>
       <c r="D231" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E231" s="2"/>
       <c r="F231" s="2" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="G231" s="2"/>
       <c r="H231" s="2"/>
@@ -12719,7 +12721,7 @@
       <c r="K231" s="2"/>
       <c r="L231" s="2"/>
       <c r="M231" s="2" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="N231" s="2"/>
       <c r="O231" s="2"/>
@@ -12727,21 +12729,21 @@
       <c r="Q231" s="2"/>
     </row>
     <row r="232" spans="1:17" ht="15">
-      <c r="A232" s="2" t="s">
+      <c r="A232" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B232" s="2" t="s">
         <v>1050</v>
       </c>
-      <c r="B232" s="2" t="s">
+      <c r="C232" s="2" t="s">
         <v>1051</v>
-      </c>
-      <c r="C232" s="2" t="s">
-        <v>1052</v>
       </c>
       <c r="D232" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E232" s="2"/>
       <c r="F232" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="G232" s="2"/>
       <c r="H232" s="2"/>
@@ -12750,7 +12752,7 @@
       <c r="K232" s="2"/>
       <c r="L232" s="2"/>
       <c r="M232" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="N232" s="2"/>
       <c r="O232" s="2"/>
@@ -12758,21 +12760,21 @@
       <c r="Q232" s="2"/>
     </row>
     <row r="233" spans="1:17" ht="15">
-      <c r="A233" s="2" t="s">
+      <c r="A233" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B233" s="2" t="s">
         <v>1050</v>
       </c>
-      <c r="B233" s="2" t="s">
+      <c r="C233" s="2" t="s">
         <v>1051</v>
-      </c>
-      <c r="C233" s="2" t="s">
-        <v>1052</v>
       </c>
       <c r="D233" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E233" s="2"/>
       <c r="F233" s="2" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="G233" s="2"/>
       <c r="H233" s="2"/>
@@ -12781,7 +12783,7 @@
       <c r="K233" s="2"/>
       <c r="L233" s="2"/>
       <c r="M233" s="2" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="N233" s="2"/>
       <c r="O233" s="2"/>
@@ -12789,21 +12791,21 @@
       <c r="Q233" s="2"/>
     </row>
     <row r="234" spans="1:17" ht="15">
-      <c r="A234" s="2" t="s">
+      <c r="A234" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B234" s="2" t="s">
         <v>1050</v>
       </c>
-      <c r="B234" s="2" t="s">
+      <c r="C234" s="2" t="s">
         <v>1051</v>
-      </c>
-      <c r="C234" s="2" t="s">
-        <v>1052</v>
       </c>
       <c r="D234" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E234" s="2"/>
       <c r="F234" s="2" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="G234" s="2"/>
       <c r="H234" s="2"/>
@@ -12812,7 +12814,7 @@
       <c r="K234" s="2"/>
       <c r="L234" s="2"/>
       <c r="M234" s="2" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="N234" s="2"/>
       <c r="O234" s="2"/>
@@ -12820,21 +12822,21 @@
       <c r="Q234" s="2"/>
     </row>
     <row r="235" spans="1:17" ht="15">
-      <c r="A235" s="2" t="s">
+      <c r="A235" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B235" s="2" t="s">
         <v>1050</v>
       </c>
-      <c r="B235" s="2" t="s">
+      <c r="C235" s="2" t="s">
         <v>1051</v>
-      </c>
-      <c r="C235" s="2" t="s">
-        <v>1052</v>
       </c>
       <c r="D235" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E235" s="2"/>
       <c r="F235" s="2" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="G235" s="2"/>
       <c r="H235" s="2"/>
@@ -12843,7 +12845,7 @@
       <c r="K235" s="2"/>
       <c r="L235" s="2"/>
       <c r="M235" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="N235" s="2"/>
       <c r="O235" s="2"/>
@@ -12851,21 +12853,21 @@
       <c r="Q235" s="2"/>
     </row>
     <row r="236" spans="1:17" ht="15">
-      <c r="A236" s="2" t="s">
+      <c r="A236" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B236" s="2" t="s">
         <v>1050</v>
       </c>
-      <c r="B236" s="2" t="s">
+      <c r="C236" s="2" t="s">
         <v>1051</v>
-      </c>
-      <c r="C236" s="2" t="s">
-        <v>1052</v>
       </c>
       <c r="D236" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E236" s="2"/>
       <c r="F236" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="G236" s="2"/>
       <c r="H236" s="2"/>
@@ -12874,7 +12876,7 @@
       <c r="K236" s="2"/>
       <c r="L236" s="2"/>
       <c r="M236" s="2" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="N236" s="2"/>
       <c r="O236" s="2"/>
@@ -12882,21 +12884,21 @@
       <c r="Q236" s="2"/>
     </row>
     <row r="237" spans="1:17" ht="15">
-      <c r="A237" s="2" t="s">
+      <c r="A237" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B237" s="2" t="s">
         <v>1050</v>
       </c>
-      <c r="B237" s="2" t="s">
+      <c r="C237" s="2" t="s">
         <v>1051</v>
-      </c>
-      <c r="C237" s="2" t="s">
-        <v>1052</v>
       </c>
       <c r="D237" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E237" s="2"/>
       <c r="F237" s="2" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="G237" s="2"/>
       <c r="H237" s="2"/>
@@ -12905,7 +12907,7 @@
       <c r="K237" s="2"/>
       <c r="L237" s="2"/>
       <c r="M237" s="2" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="N237" s="2"/>
       <c r="O237" s="2"/>
@@ -12913,21 +12915,21 @@
       <c r="Q237" s="2"/>
     </row>
     <row r="238" spans="1:17" ht="15">
-      <c r="A238" s="2" t="s">
+      <c r="A238" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B238" s="2" t="s">
         <v>1050</v>
       </c>
-      <c r="B238" s="2" t="s">
+      <c r="C238" s="2" t="s">
         <v>1051</v>
-      </c>
-      <c r="C238" s="2" t="s">
-        <v>1052</v>
       </c>
       <c r="D238" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E238" s="2"/>
       <c r="F238" s="2" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="G238" s="2"/>
       <c r="H238" s="2"/>
@@ -12936,7 +12938,7 @@
       <c r="K238" s="2"/>
       <c r="L238" s="2"/>
       <c r="M238" s="2" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="N238" s="2"/>
       <c r="O238" s="2"/>
@@ -12944,21 +12946,21 @@
       <c r="Q238" s="2"/>
     </row>
     <row r="239" spans="1:17" ht="15">
-      <c r="A239" s="2" t="s">
+      <c r="A239" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B239" s="2" t="s">
         <v>1050</v>
       </c>
-      <c r="B239" s="2" t="s">
+      <c r="C239" s="2" t="s">
         <v>1051</v>
-      </c>
-      <c r="C239" s="2" t="s">
-        <v>1052</v>
       </c>
       <c r="D239" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E239" s="2"/>
       <c r="F239" s="2" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="G239" s="2"/>
       <c r="H239" s="2"/>
@@ -12967,7 +12969,7 @@
       <c r="K239" s="2"/>
       <c r="L239" s="2"/>
       <c r="M239" s="2" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="N239" s="2"/>
       <c r="O239" s="2"/>
@@ -12975,21 +12977,21 @@
       <c r="Q239" s="2"/>
     </row>
     <row r="240" spans="1:17" ht="15">
-      <c r="A240" s="2" t="s">
+      <c r="A240" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B240" s="2" t="s">
         <v>1050</v>
       </c>
-      <c r="B240" s="2" t="s">
+      <c r="C240" s="2" t="s">
         <v>1051</v>
-      </c>
-      <c r="C240" s="2" t="s">
-        <v>1052</v>
       </c>
       <c r="D240" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E240" s="2"/>
       <c r="F240" s="2" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="G240" s="2"/>
       <c r="H240" s="2"/>
@@ -12998,7 +13000,7 @@
       <c r="K240" s="2"/>
       <c r="L240" s="2"/>
       <c r="M240" s="2" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="N240" s="2"/>
       <c r="O240" s="2"/>
